--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/28.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/28.xlsx
@@ -426,13 +426,13 @@
         <v>-21.47068891389276</v>
       </c>
       <c r="E2">
-        <v>-10.2749646889434</v>
+        <v>-10.63009667757292</v>
       </c>
       <c r="F2">
-        <v>-1.1926816514172</v>
+        <v>-2.101869004852959</v>
       </c>
       <c r="G2">
-        <v>-10.47896695194406</v>
+        <v>-10.65030423632904</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.79558985551884</v>
       </c>
       <c r="E3">
-        <v>-10.83040919682821</v>
+        <v>-12.79640543099223</v>
       </c>
       <c r="F3">
-        <v>-1.110020913013796</v>
+        <v>-1.853760093169511</v>
       </c>
       <c r="G3">
-        <v>-10.31939203586011</v>
+        <v>-10.90364373372177</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.03062686361885</v>
       </c>
       <c r="E4">
-        <v>-11.45949122055176</v>
+        <v>-13.61452407369196</v>
       </c>
       <c r="F4">
-        <v>-1.338533839552554</v>
+        <v>-1.940959732726565</v>
       </c>
       <c r="G4">
-        <v>-9.150875397954639</v>
+        <v>-9.616218921136754</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.26967855886017</v>
       </c>
       <c r="E5">
-        <v>-12.69043913921274</v>
+        <v>-13.80318935779953</v>
       </c>
       <c r="F5">
-        <v>-1.187162436301894</v>
+        <v>-1.878953686872322</v>
       </c>
       <c r="G5">
-        <v>-8.869207562382368</v>
+        <v>-9.810223510829124</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.53079663497588</v>
       </c>
       <c r="E6">
-        <v>-12.90623903957427</v>
+        <v>-12.47442187209885</v>
       </c>
       <c r="F6">
-        <v>-1.084974603961121</v>
+        <v>-1.610302525759709</v>
       </c>
       <c r="G6">
-        <v>-8.501932329710083</v>
+        <v>-8.681737989584519</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.85483704882058</v>
       </c>
       <c r="E7">
-        <v>-14.20822965846759</v>
+        <v>-14.25126374696248</v>
       </c>
       <c r="F7">
-        <v>-1.225248979862297</v>
+        <v>-1.954803697986379</v>
       </c>
       <c r="G7">
-        <v>-8.250089198901106</v>
+        <v>-8.917644154167444</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.24441186112629</v>
       </c>
       <c r="E8">
-        <v>-14.44648173295914</v>
+        <v>-14.43752893984598</v>
       </c>
       <c r="F8">
-        <v>-1.368571197797736</v>
+        <v>-2.335530559322811</v>
       </c>
       <c r="G8">
-        <v>-8.219082629380292</v>
+        <v>-7.885111484833075</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.71326017520554</v>
       </c>
       <c r="E9">
-        <v>-15.20634155755019</v>
+        <v>-16.40916312414954</v>
       </c>
       <c r="F9">
-        <v>-1.417458615701436</v>
+        <v>-1.84033897738912</v>
       </c>
       <c r="G9">
-        <v>-7.712327492047434</v>
+        <v>-6.696029738037651</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.25209117079065</v>
       </c>
       <c r="E10">
-        <v>-15.6925275839617</v>
+        <v>-16.81371434962477</v>
       </c>
       <c r="F10">
-        <v>-1.164224831675626</v>
+        <v>-2.183345923084572</v>
       </c>
       <c r="G10">
-        <v>-6.481162090356793</v>
+        <v>-6.802119480389135</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.8413438878</v>
       </c>
       <c r="E11">
-        <v>-16.29565239467328</v>
+        <v>-18.91032083111802</v>
       </c>
       <c r="F11">
-        <v>-1.134825706914366</v>
+        <v>-2.071943297874816</v>
       </c>
       <c r="G11">
-        <v>-6.106345434946049</v>
+        <v>-7.611521380376626</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.45926352841552</v>
       </c>
       <c r="E12">
-        <v>-16.85286300742108</v>
+        <v>-18.7714506471988</v>
       </c>
       <c r="F12">
-        <v>-0.988618768653954</v>
+        <v>-1.88432324177862</v>
       </c>
       <c r="G12">
-        <v>-5.110490299641265</v>
+        <v>-5.790181714854572</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.06335855606732</v>
       </c>
       <c r="E13">
-        <v>-17.17590170075825</v>
+        <v>-19.15792873290942</v>
       </c>
       <c r="F13">
-        <v>-1.286490095759383</v>
+        <v>-1.662801585003569</v>
       </c>
       <c r="G13">
-        <v>-4.144337378914823</v>
+        <v>-5.781829208458991</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.63076299202922</v>
       </c>
       <c r="E14">
-        <v>-19.2601726190546</v>
+        <v>-20.04377976134188</v>
       </c>
       <c r="F14">
-        <v>-1.190016274361515</v>
+        <v>-1.682596325240647</v>
       </c>
       <c r="G14">
-        <v>-4.138646551132815</v>
+        <v>-4.640280274516422</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.14650741863228</v>
       </c>
       <c r="E15">
-        <v>-19.9237072730285</v>
+        <v>-20.43943706386604</v>
       </c>
       <c r="F15">
-        <v>-1.111624415253178</v>
+        <v>-1.455457263583533</v>
       </c>
       <c r="G15">
-        <v>-3.426448889269405</v>
+        <v>-4.834662266400269</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.60154341236435</v>
       </c>
       <c r="E16">
-        <v>-19.88695417798224</v>
+        <v>-20.73701667633209</v>
       </c>
       <c r="F16">
-        <v>-1.031914120970238</v>
+        <v>-1.413211908289185</v>
       </c>
       <c r="G16">
-        <v>-3.161118595933437</v>
+        <v>-3.986351524689723</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.01033000103129</v>
       </c>
       <c r="E17">
-        <v>-21.45234348753171</v>
+        <v>-23.48590002541616</v>
       </c>
       <c r="F17">
-        <v>-0.9718734541570551</v>
+        <v>-1.05085999483664</v>
       </c>
       <c r="G17">
-        <v>-2.546509195476663</v>
+        <v>-3.426717043458086</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.38722623355968</v>
       </c>
       <c r="E18">
-        <v>-22.48715866844649</v>
+        <v>-23.76839529096265</v>
       </c>
       <c r="F18">
-        <v>-0.7905304164567034</v>
+        <v>-0.7114155955979681</v>
       </c>
       <c r="G18">
-        <v>-2.766653852747119</v>
+        <v>-3.451883810647626</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.74938270908339</v>
       </c>
       <c r="E19">
-        <v>-22.9457210034112</v>
+        <v>-24.28541569689239</v>
       </c>
       <c r="F19">
-        <v>-0.7040339423261048</v>
+        <v>-0.7172135429543919</v>
       </c>
       <c r="G19">
-        <v>-2.720607474841395</v>
+        <v>-3.233301730871706</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.12238511987872</v>
       </c>
       <c r="E20">
-        <v>-22.98032307330381</v>
+        <v>-25.4200882581503</v>
       </c>
       <c r="F20">
-        <v>-0.2619361012075214</v>
+        <v>-0.3181988375594231</v>
       </c>
       <c r="G20">
-        <v>-1.99884895746057</v>
+        <v>-3.173185534424081</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.52012532152575</v>
       </c>
       <c r="E21">
-        <v>-24.19832408477687</v>
+        <v>-24.72332819038213</v>
       </c>
       <c r="F21">
-        <v>-0.2242811175090753</v>
+        <v>-0.2076735854268195</v>
       </c>
       <c r="G21">
-        <v>-1.922411771504337</v>
+        <v>-2.730274267816067</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.968527393104145</v>
       </c>
       <c r="E22">
-        <v>-25.18362945936579</v>
+        <v>-26.96899845078586</v>
       </c>
       <c r="F22">
-        <v>-0.09167742120933038</v>
+        <v>-0.01290784824016087</v>
       </c>
       <c r="G22">
-        <v>-1.26329870736314</v>
+        <v>-2.587804940533532</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.489925199698771</v>
       </c>
       <c r="E23">
-        <v>-25.25882024178915</v>
+        <v>-26.35375997210376</v>
       </c>
       <c r="F23">
-        <v>-0.2845157882968993</v>
+        <v>-0.4131602198080456</v>
       </c>
       <c r="G23">
-        <v>-2.106219880935752</v>
+        <v>-3.32308703644228</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.095883920394582</v>
       </c>
       <c r="E24">
-        <v>-25.21099049932013</v>
+        <v>-27.25610823134616</v>
       </c>
       <c r="F24">
-        <v>-0.2171045541532615</v>
+        <v>-0.1304291212542182</v>
       </c>
       <c r="G24">
-        <v>-0.9788202186280279</v>
+        <v>-3.409502206653876</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.798761773470957</v>
       </c>
       <c r="E25">
-        <v>-25.49728515455906</v>
+        <v>-27.16374094701171</v>
       </c>
       <c r="F25">
-        <v>-0.1838419788112867</v>
+        <v>0.008898198509524884</v>
       </c>
       <c r="G25">
-        <v>-1.995743665744733</v>
+        <v>-2.955460885942833</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.597640920132605</v>
       </c>
       <c r="E26">
-        <v>-26.42720729203416</v>
+        <v>-27.05211859119665</v>
       </c>
       <c r="F26">
-        <v>0.09269366220134148</v>
+        <v>-0.2048284577497326</v>
       </c>
       <c r="G26">
-        <v>-1.839072098098725</v>
+        <v>-3.338404930652488</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.481433480259842</v>
       </c>
       <c r="E27">
-        <v>-25.92700111009491</v>
+        <v>-27.54380671352747</v>
       </c>
       <c r="F27">
-        <v>0.1048303924843117</v>
+        <v>-0.00103638869802677</v>
       </c>
       <c r="G27">
-        <v>-1.948631292175365</v>
+        <v>-3.762750657876269</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.438403461205926</v>
       </c>
       <c r="E28">
-        <v>-26.06852497978263</v>
+        <v>-28.02663714069929</v>
       </c>
       <c r="F28">
-        <v>0.07779653250776032</v>
+        <v>-0.2765291593653381</v>
       </c>
       <c r="G28">
-        <v>-1.854681320316388</v>
+        <v>-3.046679657731911</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.445002047953491</v>
       </c>
       <c r="E29">
-        <v>-25.75511835065978</v>
+        <v>-27.42466256238566</v>
       </c>
       <c r="F29">
-        <v>0.01464942654144324</v>
+        <v>-0.32968387285819</v>
       </c>
       <c r="G29">
-        <v>-2.356000541873763</v>
+        <v>-3.760314096359365</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.485107285003522</v>
       </c>
       <c r="E30">
-        <v>-26.03739172097989</v>
+        <v>-27.53414747846911</v>
       </c>
       <c r="F30">
-        <v>0.357746643474076</v>
+        <v>0.07305095773214602</v>
       </c>
       <c r="G30">
-        <v>-1.951382355518499</v>
+        <v>-2.855363231017429</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.545716787490781</v>
       </c>
       <c r="E31">
-        <v>-25.31735076833828</v>
+        <v>-26.81212305421214</v>
       </c>
       <c r="F31">
-        <v>-0.01257289443904542</v>
+        <v>-0.07430575102287508</v>
       </c>
       <c r="G31">
-        <v>-2.301399714294563</v>
+        <v>-3.410362948494086</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.611244547439414</v>
       </c>
       <c r="E32">
-        <v>-24.71921633598316</v>
+        <v>-25.66250652872891</v>
       </c>
       <c r="F32">
-        <v>0.158602751284185</v>
+        <v>0.01502238928452923</v>
       </c>
       <c r="G32">
-        <v>-2.457634289929389</v>
+        <v>-2.509397979981433</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.67491898744977</v>
       </c>
       <c r="E33">
-        <v>-25.08870811569101</v>
+        <v>-25.65042908855045</v>
       </c>
       <c r="F33">
-        <v>-0.01532537532007918</v>
+        <v>0.3491645411183096</v>
       </c>
       <c r="G33">
-        <v>-2.574400541645023</v>
+        <v>-2.626213889880156</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.734299342129177</v>
       </c>
       <c r="E34">
-        <v>-24.52391683745436</v>
+        <v>-26.47031836458719</v>
       </c>
       <c r="F34">
-        <v>0.450960406245011</v>
+        <v>-0.3241258569479553</v>
       </c>
       <c r="G34">
-        <v>-2.177456199849789</v>
+        <v>-2.89646696443302</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.787889938539161</v>
       </c>
       <c r="E35">
-        <v>-24.14466166778598</v>
+        <v>-26.19127379623454</v>
       </c>
       <c r="F35">
-        <v>0.4724164539873846</v>
+        <v>-0.3159214684530212</v>
       </c>
       <c r="G35">
-        <v>-2.179482253719824</v>
+        <v>-2.649172523195002</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.842411640863455</v>
       </c>
       <c r="E36">
-        <v>-23.83709224165901</v>
+        <v>-26.03914424042086</v>
       </c>
       <c r="F36">
-        <v>0.3976116887775178</v>
+        <v>0.3484550408681928</v>
       </c>
       <c r="G36">
-        <v>-1.904018380488147</v>
+        <v>-2.510404385825372</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.901993224724205</v>
       </c>
       <c r="E37">
-        <v>-23.54010585928798</v>
+        <v>-23.72911983589413</v>
       </c>
       <c r="F37">
-        <v>0.4263147747889423</v>
+        <v>-0.04734315781251849</v>
       </c>
       <c r="G37">
-        <v>-1.729340755654042</v>
+        <v>-1.449665868496412</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.973566047296258</v>
       </c>
       <c r="E38">
-        <v>-23.03211975900355</v>
+        <v>-24.99794391115527</v>
       </c>
       <c r="F38">
-        <v>0.6856165280297585</v>
+        <v>-0.5935364050470214</v>
       </c>
       <c r="G38">
-        <v>-1.429567546527496</v>
+        <v>-2.556785128830561</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.06840813829999</v>
       </c>
       <c r="E39">
-        <v>-22.70004223154707</v>
+        <v>-24.64496294767939</v>
       </c>
       <c r="F39">
-        <v>0.2561463660279314</v>
+        <v>0.2005527454253028</v>
       </c>
       <c r="G39">
-        <v>-2.390658643124393</v>
+        <v>-1.524302117679281</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.188862812164983</v>
       </c>
       <c r="E40">
-        <v>-21.63411190572559</v>
+        <v>-23.25158319483727</v>
       </c>
       <c r="F40">
-        <v>0.3946786654221239</v>
+        <v>0.4392726565890679</v>
       </c>
       <c r="G40">
-        <v>-1.988000299728378</v>
+        <v>-1.63986333081862</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.339348390388862</v>
       </c>
       <c r="E41">
-        <v>-21.79327418167318</v>
+        <v>-22.82807577716594</v>
       </c>
       <c r="F41">
-        <v>0.3189537670753868</v>
+        <v>-0.05611688858405303</v>
       </c>
       <c r="G41">
-        <v>-1.326520195526602</v>
+        <v>-1.351329423797901</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.525606502322287</v>
       </c>
       <c r="E42">
-        <v>-20.92339055259177</v>
+        <v>-23.23014087041096</v>
       </c>
       <c r="F42">
-        <v>0.3516612534939999</v>
+        <v>-0.0218660807508441</v>
       </c>
       <c r="G42">
-        <v>-1.60870116565746</v>
+        <v>-2.526506879328386</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.746320413082742</v>
       </c>
       <c r="E43">
-        <v>-21.00800508942509</v>
+        <v>-22.01870161777501</v>
       </c>
       <c r="F43">
-        <v>0.5108466617314382</v>
+        <v>-0.2912853392324452</v>
       </c>
       <c r="G43">
-        <v>-1.890753024512287</v>
+        <v>-3.096632479373974</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.00381713983262</v>
       </c>
       <c r="E44">
-        <v>-19.32936317341779</v>
+        <v>-21.72627088025569</v>
       </c>
       <c r="F44">
-        <v>0.6843764862979694</v>
+        <v>-0.2442682780148789</v>
       </c>
       <c r="G44">
-        <v>-1.652552651870647</v>
+        <v>-2.055032225807541</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.29147055107773</v>
       </c>
       <c r="E45">
-        <v>-20.01435826571404</v>
+        <v>-21.16293324217551</v>
       </c>
       <c r="F45">
-        <v>0.3200330626567587</v>
+        <v>0.2271225795686304</v>
       </c>
       <c r="G45">
-        <v>-2.06325893147263</v>
+        <v>-2.422257800296737</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.60000573459543</v>
       </c>
       <c r="E46">
-        <v>-19.60885153222319</v>
+        <v>-19.96510205393261</v>
       </c>
       <c r="F46">
-        <v>0.5687469499999045</v>
+        <v>0.3320003364067769</v>
       </c>
       <c r="G46">
-        <v>-2.198547685480486</v>
+        <v>-2.174238349585618</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.92636937011561</v>
       </c>
       <c r="E47">
-        <v>-17.58711431149876</v>
+        <v>-20.32897852587095</v>
       </c>
       <c r="F47">
-        <v>0.9091502831703747</v>
+        <v>-0.07605574605943567</v>
       </c>
       <c r="G47">
-        <v>-2.48270174075275</v>
+        <v>-3.2778451211026</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.25947734024374</v>
       </c>
       <c r="E48">
-        <v>-18.53841990323809</v>
+        <v>-21.55681085441466</v>
       </c>
       <c r="F48">
-        <v>0.5935842098717413</v>
+        <v>0.6152873157369235</v>
       </c>
       <c r="G48">
-        <v>-1.470674590488627</v>
+        <v>-2.484777452805873</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.5938031524073</v>
       </c>
       <c r="E49">
-        <v>-17.44194049176087</v>
+        <v>-19.76070937959641</v>
       </c>
       <c r="F49">
-        <v>0.8102240931624497</v>
+        <v>0.2031009282432449</v>
       </c>
       <c r="G49">
-        <v>-1.940960758160874</v>
+        <v>-3.001133172202618</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.92772095336621</v>
       </c>
       <c r="E50">
-        <v>-18.12659594850654</v>
+        <v>-18.05792164018022</v>
       </c>
       <c r="F50">
-        <v>1.073101854360328</v>
+        <v>0.04277762730556326</v>
       </c>
       <c r="G50">
-        <v>-2.793489134888451</v>
+        <v>-3.849877595378808</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.25394395170985</v>
       </c>
       <c r="E51">
-        <v>-16.75426454285208</v>
+        <v>-18.40158753262232</v>
       </c>
       <c r="F51">
-        <v>0.6905117630143818</v>
+        <v>0.04317355378442313</v>
       </c>
       <c r="G51">
-        <v>-2.362684533317552</v>
+        <v>-3.562535484752226</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.57416633296046</v>
       </c>
       <c r="E52">
-        <v>-16.00050910122336</v>
+        <v>-19.01718828922503</v>
       </c>
       <c r="F52">
-        <v>0.5894222307259664</v>
+        <v>0.1384128764212052</v>
       </c>
       <c r="G52">
-        <v>-3.046577030820194</v>
+        <v>-3.90678256265334</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.88390469622443</v>
       </c>
       <c r="E53">
-        <v>-15.79043772048154</v>
+        <v>-17.29492358310185</v>
       </c>
       <c r="F53">
-        <v>0.8972899095696487</v>
+        <v>0.4543717087868676</v>
       </c>
       <c r="G53">
-        <v>-2.508302189407934</v>
+        <v>-3.487280163553513</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.17851188981712</v>
       </c>
       <c r="E54">
-        <v>-14.77314320550244</v>
+        <v>-16.83411965350334</v>
       </c>
       <c r="F54">
-        <v>1.017776671910366</v>
+        <v>0.6399487842521466</v>
       </c>
       <c r="G54">
-        <v>-3.712427055133808</v>
+        <v>-4.065844344178703</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.46193009341407</v>
       </c>
       <c r="E55">
-        <v>-15.39020665920963</v>
+        <v>-16.45710607846875</v>
       </c>
       <c r="F55">
-        <v>1.005864036014431</v>
+        <v>0.4600421678170985</v>
       </c>
       <c r="G55">
-        <v>-3.563167798950227</v>
+        <v>-3.431709346131307</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.72727376202164</v>
       </c>
       <c r="E56">
-        <v>-15.08313989369752</v>
+        <v>-15.96748294028542</v>
       </c>
       <c r="F56">
-        <v>0.7759542808582555</v>
+        <v>0.2343933734264129</v>
       </c>
       <c r="G56">
-        <v>-3.230166644246017</v>
+        <v>-3.565620913194826</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.9733499137303</v>
       </c>
       <c r="E57">
-        <v>-14.776426349158</v>
+        <v>-15.59697225392585</v>
       </c>
       <c r="F57">
-        <v>1.178297936087478</v>
+        <v>0.386510702163245</v>
       </c>
       <c r="G57">
-        <v>-4.1170982102177</v>
+        <v>-3.634453776047353</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.19973435465375</v>
       </c>
       <c r="E58">
-        <v>-14.28125130184127</v>
+        <v>-14.76767280890117</v>
       </c>
       <c r="F58">
-        <v>0.7107024297303194</v>
+        <v>-0.1197121833244395</v>
       </c>
       <c r="G58">
-        <v>-3.777707702622696</v>
+        <v>-5.492682850513506</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.40114624336551</v>
       </c>
       <c r="E59">
-        <v>-13.82608985085631</v>
+        <v>-14.9989419764729</v>
       </c>
       <c r="F59">
-        <v>1.033265315763364</v>
+        <v>0.2714655533479772</v>
       </c>
       <c r="G59">
-        <v>-3.777694460440539</v>
+        <v>-4.544112237146133</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.58137424649788</v>
       </c>
       <c r="E60">
-        <v>-13.86679177523726</v>
+        <v>-15.28850618994537</v>
       </c>
       <c r="F60">
-        <v>0.3601245779061084</v>
+        <v>0.2729344405845473</v>
       </c>
       <c r="G60">
-        <v>-4.378922635827579</v>
+        <v>-5.348151053360005</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.73601963670573</v>
       </c>
       <c r="E61">
-        <v>-14.1011403051342</v>
+        <v>-15.06503052614084</v>
       </c>
       <c r="F61">
-        <v>0.9113864759229753</v>
+        <v>-0.1373926761644055</v>
       </c>
       <c r="G61">
-        <v>-4.832844776899209</v>
+        <v>-4.796567818879875</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.86311516820658</v>
       </c>
       <c r="E62">
-        <v>-13.84183535498098</v>
+        <v>-15.04702531348634</v>
       </c>
       <c r="F62">
-        <v>0.9029358211581904</v>
+        <v>-0.2395820922110935</v>
       </c>
       <c r="G62">
-        <v>-4.355285340677183</v>
+        <v>-5.752362042613938</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.96807362865332</v>
       </c>
       <c r="E63">
-        <v>-13.05326047670729</v>
+        <v>-14.15192261265621</v>
       </c>
       <c r="F63">
-        <v>0.7490439499431084</v>
+        <v>0.04544458806716329</v>
       </c>
       <c r="G63">
-        <v>-4.448765215069583</v>
+        <v>-5.616788581689704</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-15.04610463900862</v>
       </c>
       <c r="E64">
-        <v>-12.33579169730204</v>
+        <v>-12.83196300890046</v>
       </c>
       <c r="F64">
-        <v>0.3308529414710411</v>
+        <v>-0.04347495611405764</v>
       </c>
       <c r="G64">
-        <v>-4.73917620141107</v>
+        <v>-5.99827598636208</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.10119013882558</v>
       </c>
       <c r="E65">
-        <v>-11.87794033275653</v>
+        <v>-13.27540024067955</v>
       </c>
       <c r="F65">
-        <v>0.7560249256183654</v>
+        <v>-0.1725493637812458</v>
       </c>
       <c r="G65">
-        <v>-4.737080626084711</v>
+        <v>-5.648682377415043</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.13604956835514</v>
       </c>
       <c r="E66">
-        <v>-12.11501047553208</v>
+        <v>-12.8073688665648</v>
       </c>
       <c r="F66">
-        <v>0.2854694729052505</v>
+        <v>0.1994647394613959</v>
       </c>
       <c r="G66">
-        <v>-4.549207166731072</v>
+        <v>-6.750395516883562</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.15225212720851</v>
       </c>
       <c r="E67">
-        <v>-12.60394981414025</v>
+        <v>-13.14789199804558</v>
       </c>
       <c r="F67">
-        <v>0.9005475926377077</v>
+        <v>-0.1681529961599859</v>
       </c>
       <c r="G67">
-        <v>-5.794319896778661</v>
+        <v>-6.487561374884205</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.15979382686334</v>
       </c>
       <c r="E68">
-        <v>-12.08193902985406</v>
+        <v>-13.35820791638381</v>
       </c>
       <c r="F68">
-        <v>0.5914810484160378</v>
+        <v>-0.4369625278641427</v>
       </c>
       <c r="G68">
-        <v>-6.022101982608215</v>
+        <v>-6.805360504472081</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.15854108726233</v>
       </c>
       <c r="E69">
-        <v>-12.6525086409245</v>
+        <v>-13.21354581420878</v>
       </c>
       <c r="F69">
-        <v>0.6730925816504634</v>
+        <v>-0.4766525736639284</v>
       </c>
       <c r="G69">
-        <v>-5.72118994581616</v>
+        <v>-6.629481151607221</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.15174546572657</v>
       </c>
       <c r="E70">
-        <v>-11.5295965266645</v>
+        <v>-12.68531743511007</v>
       </c>
       <c r="F70">
-        <v>0.2965696676665656</v>
+        <v>-0.1485680969567039</v>
       </c>
       <c r="G70">
-        <v>-6.255409368942813</v>
+        <v>-6.625114542040922</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.14752955867135</v>
       </c>
       <c r="E71">
-        <v>-11.36058934822424</v>
+        <v>-11.93344583866854</v>
       </c>
       <c r="F71">
-        <v>-0.1127929721798845</v>
+        <v>-0.1988697642428917</v>
       </c>
       <c r="G71">
-        <v>-6.179250268811879</v>
+        <v>-6.920660184513818</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.14179066818684</v>
       </c>
       <c r="E72">
-        <v>-12.07620598176035</v>
+        <v>-13.96256447202548</v>
       </c>
       <c r="F72">
-        <v>0.03983985283242309</v>
+        <v>-0.5429037432245069</v>
       </c>
       <c r="G72">
-        <v>-6.278692435720507</v>
+        <v>-7.309195740639303</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.1372974973097</v>
       </c>
       <c r="E73">
-        <v>-10.96288064697459</v>
+        <v>-13.16452508307575</v>
       </c>
       <c r="F73">
-        <v>0.1062763159851079</v>
+        <v>-0.5969500831477512</v>
       </c>
       <c r="G73">
-        <v>-5.724629602631463</v>
+        <v>-6.497377142408144</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.12925662137732</v>
       </c>
       <c r="E74">
-        <v>-12.20898083966525</v>
+        <v>-13.39184542131279</v>
       </c>
       <c r="F74">
-        <v>0.2024579436415764</v>
+        <v>-0.629076349495398</v>
       </c>
       <c r="G74">
-        <v>-6.356861036993778</v>
+        <v>-6.554950839881609</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.11235229469452</v>
       </c>
       <c r="E75">
-        <v>-12.31913144142782</v>
+        <v>-13.43785018875671</v>
       </c>
       <c r="F75">
-        <v>-0.1371289891294848</v>
+        <v>-0.7245556035783692</v>
       </c>
       <c r="G75">
-        <v>-6.222197976092844</v>
+        <v>-5.19636254038442</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.08723769530248</v>
       </c>
       <c r="E76">
-        <v>-11.5993803111227</v>
+        <v>-13.50590409614398</v>
       </c>
       <c r="F76">
-        <v>-0.3611695301630417</v>
+        <v>-1.058503751437508</v>
       </c>
       <c r="G76">
-        <v>-6.079109576794465</v>
+        <v>-6.997365524658732</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.04407611350634</v>
       </c>
       <c r="E77">
-        <v>-12.41483168263192</v>
+        <v>-15.30280258238758</v>
       </c>
       <c r="F77">
-        <v>-0.4985267197679781</v>
+        <v>-0.8958634887455388</v>
       </c>
       <c r="G77">
-        <v>-6.318855974202945</v>
+        <v>-6.280850911412112</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.97960482677425</v>
       </c>
       <c r="E78">
-        <v>-13.83887373297997</v>
+        <v>-14.22236755431953</v>
       </c>
       <c r="F78">
-        <v>-0.2813246208772888</v>
+        <v>-0.9240296984516294</v>
       </c>
       <c r="G78">
-        <v>-6.566100757257875</v>
+        <v>-5.976092020703424</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.89483889273178</v>
       </c>
       <c r="E79">
-        <v>-12.77125428635363</v>
+        <v>-13.47449007195277</v>
       </c>
       <c r="F79">
-        <v>-0.5046968380145302</v>
+        <v>-0.7239181619474049</v>
       </c>
       <c r="G79">
-        <v>-6.381253136527128</v>
+        <v>-5.467112196768175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.78278672167835</v>
       </c>
       <c r="E80">
-        <v>-14.23125242032258</v>
+        <v>-16.87774697209323</v>
       </c>
       <c r="F80">
-        <v>-0.4590758135614237</v>
+        <v>-1.012430578945544</v>
       </c>
       <c r="G80">
-        <v>-6.54718098950094</v>
+        <v>-5.258882192893557</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.64634797967995</v>
       </c>
       <c r="E81">
-        <v>-15.24049530851604</v>
+        <v>-15.97431187908899</v>
       </c>
       <c r="F81">
-        <v>-0.3107498767861537</v>
+        <v>-1.099697526004004</v>
       </c>
       <c r="G81">
-        <v>-5.96725286411357</v>
+        <v>-5.64528906823729</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.48168898741832</v>
       </c>
       <c r="E82">
-        <v>-16.24059973616203</v>
+        <v>-15.62245397716701</v>
       </c>
       <c r="F82">
-        <v>-0.5909644666403477</v>
+        <v>-1.310101567252669</v>
       </c>
       <c r="G82">
-        <v>-5.504296244265269</v>
+        <v>-5.627650481604053</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.28994676393917</v>
       </c>
       <c r="E83">
-        <v>-17.4092539663735</v>
+        <v>-18.29929836173707</v>
       </c>
       <c r="F83">
-        <v>-0.4895692791102526</v>
+        <v>-1.148695011468827</v>
       </c>
       <c r="G83">
-        <v>-5.966176936813307</v>
+        <v>-5.282751226231702</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.0776279533839</v>
       </c>
       <c r="E84">
-        <v>-17.67903780538046</v>
+        <v>-17.80486145568358</v>
       </c>
       <c r="F84">
-        <v>-0.7642044730243535</v>
+        <v>-1.115972479844017</v>
       </c>
       <c r="G84">
-        <v>-5.579296653457458</v>
+        <v>-5.036661823569979</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.84224039825223</v>
       </c>
       <c r="E85">
-        <v>-17.52693089193682</v>
+        <v>-18.65826143937708</v>
       </c>
       <c r="F85">
-        <v>-0.6372253082832917</v>
+        <v>-1.285522451445049</v>
       </c>
       <c r="G85">
-        <v>-5.18187559310457</v>
+        <v>-4.024399624572567</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.58840441318891</v>
       </c>
       <c r="E86">
-        <v>-19.18610489818514</v>
+        <v>-19.42499548751178</v>
       </c>
       <c r="F86">
-        <v>-0.5149663790231973</v>
+        <v>-0.9566690855158787</v>
       </c>
       <c r="G86">
-        <v>-4.999130168791261</v>
+        <v>-5.129919891411248</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.32056791629256</v>
       </c>
       <c r="E87">
-        <v>-20.89338941229095</v>
+        <v>-21.84247152329251</v>
       </c>
       <c r="F87">
-        <v>-0.6685739750264579</v>
+        <v>-1.154643410887218</v>
       </c>
       <c r="G87">
-        <v>-4.866936774862624</v>
+        <v>-4.870472437498565</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.03549072906429</v>
       </c>
       <c r="E88">
-        <v>-22.95514928629517</v>
+        <v>-22.76692779264036</v>
       </c>
       <c r="F88">
-        <v>-0.7060484162505438</v>
+        <v>-0.9496596031341437</v>
       </c>
       <c r="G88">
-        <v>-5.152477948715842</v>
+        <v>-4.885591698976416</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.73747606548881</v>
       </c>
       <c r="E89">
-        <v>-23.59780767509371</v>
+        <v>-24.81334066823259</v>
       </c>
       <c r="F89">
-        <v>-0.4365610584145789</v>
+        <v>-1.331050037249145</v>
       </c>
       <c r="G89">
-        <v>-4.52745357199252</v>
+        <v>-6.165061270630563</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.42022929590715</v>
       </c>
       <c r="E90">
-        <v>-24.29484850825036</v>
+        <v>-24.51436628577218</v>
       </c>
       <c r="F90">
-        <v>-0.6803591225962006</v>
+        <v>-1.42542703201497</v>
       </c>
       <c r="G90">
-        <v>-4.611740061422364</v>
+        <v>-4.218986870279849</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.08417270998641</v>
       </c>
       <c r="E91">
-        <v>-26.35923036870503</v>
+        <v>-27.84842357460143</v>
       </c>
       <c r="F91">
-        <v>-0.6844727987115545</v>
+        <v>-0.9851385749047759</v>
       </c>
       <c r="G91">
-        <v>-4.710434045039118</v>
+        <v>-5.006555722435847</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.73128966957354</v>
       </c>
       <c r="E92">
-        <v>-28.63177259387027</v>
+        <v>-30.90574581682194</v>
       </c>
       <c r="F92">
-        <v>-0.8847244931892955</v>
+        <v>-1.567317579802852</v>
       </c>
       <c r="G92">
-        <v>-4.842442048417556</v>
+        <v>-3.471263744234519</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.35641878222782</v>
       </c>
       <c r="E93">
-        <v>-30.94004447895604</v>
+        <v>-31.46928044352146</v>
       </c>
       <c r="F93">
-        <v>-0.8348472590884455</v>
+        <v>-1.37450455200993</v>
       </c>
       <c r="G93">
-        <v>-4.435443579819556</v>
+        <v>-4.39786226685775</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.96387909793344</v>
       </c>
       <c r="E94">
-        <v>-33.23517473247154</v>
+        <v>-33.60653903618157</v>
       </c>
       <c r="F94">
-        <v>-0.768316565433792</v>
+        <v>-1.182701136738101</v>
       </c>
       <c r="G94">
-        <v>-4.893497281724196</v>
+        <v>-3.560016159596841</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.55827282708981</v>
       </c>
       <c r="E95">
-        <v>-35.38252276522073</v>
+        <v>-35.06453105616512</v>
       </c>
       <c r="F95">
-        <v>-0.7658903279713388</v>
+        <v>-1.679985586039045</v>
       </c>
       <c r="G95">
-        <v>-4.820175319120418</v>
+        <v>-3.82170816338515</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.14286130266096</v>
       </c>
       <c r="E96">
-        <v>-36.41278003704679</v>
+        <v>-37.1331130762619</v>
       </c>
       <c r="F96">
-        <v>-0.6174353191639604</v>
+        <v>-1.278189893056564</v>
       </c>
       <c r="G96">
-        <v>-4.449851074006465</v>
+        <v>-4.134183935745878</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.731427906191485</v>
       </c>
       <c r="E97">
-        <v>-39.74476102054352</v>
+        <v>-40.11697894160399</v>
       </c>
       <c r="F97">
-        <v>-1.208228100536111</v>
+        <v>-1.366568601667663</v>
       </c>
       <c r="G97">
-        <v>-5.279877672703615</v>
+        <v>-5.282933306236362</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.329850611472992</v>
       </c>
       <c r="E98">
-        <v>-41.59635215161476</v>
+        <v>-41.20944838934742</v>
       </c>
       <c r="F98">
-        <v>-0.6851593352258976</v>
+        <v>-1.253671749926689</v>
       </c>
       <c r="G98">
-        <v>-5.224522040741461</v>
+        <v>-4.201056955639156</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.953925341626444</v>
       </c>
       <c r="E99">
-        <v>-43.63153441166796</v>
+        <v>-44.76827648554738</v>
       </c>
       <c r="F99">
-        <v>-0.8976396149297041</v>
+        <v>-1.017990970414652</v>
       </c>
       <c r="G99">
-        <v>-5.270078457907372</v>
+        <v>-4.963326618784043</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.618806970327945</v>
       </c>
       <c r="E100">
-        <v>-47.62242194870275</v>
+        <v>-47.46156149500229</v>
       </c>
       <c r="F100">
-        <v>-0.6687885671779999</v>
+        <v>-1.331236914547166</v>
       </c>
       <c r="G100">
-        <v>-5.275603758412416</v>
+        <v>-5.429067407430871</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.334452759059394</v>
       </c>
       <c r="E101">
-        <v>-49.5512405433823</v>
+        <v>-49.48831739704572</v>
       </c>
       <c r="F101">
-        <v>-1.200065680247936</v>
+        <v>-1.660879757875183</v>
       </c>
       <c r="G101">
-        <v>-5.622416509106466</v>
+        <v>-5.126198838225108</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.111031785750985</v>
       </c>
       <c r="E102">
-        <v>-51.3933648995405</v>
+        <v>-52.11584556755374</v>
       </c>
       <c r="F102">
-        <v>-0.8029078700388205</v>
+        <v>-1.690171982487151</v>
       </c>
       <c r="G102">
-        <v>-5.476143364999308</v>
+        <v>-5.186493804131853</v>
       </c>
     </row>
   </sheetData>
